--- a/jogos_2025-02-24.xlsx
+++ b/jogos_2025-02-24.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ma'an</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Livyi Bereh</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
-        <v>1.57</v>
+        <v>29</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>19</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['25', '35']</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="AH11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.11</v>
       </c>
-      <c r="AI11" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45712.54166666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Ma'an</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Livyi Bereh</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>29</v>
+        <v>1.57</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>4.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.2</v>
       </c>
-      <c r="S12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X12" t="n">
-        <v>5.6</v>
+        <v>4.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '35']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.8</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45712.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Stal Stalowa Wola</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
         <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="O17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X17" t="n">
         <v>3</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.27</v>
       </c>
-      <c r="X17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['15', '21', '57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['8', '51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45712.625</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.44</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X18" t="n">
         <v>3.4</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['15', '21', '57']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['8', '39', '69']</t>
+          <t>['8', '51']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45712.625</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>4</v>
       </c>
-      <c r="H19" t="n">
-        <v>3</v>
-      </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>2</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.65</v>
+        <v>2.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['7', '9', '38', '89']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['19', '23', '67']</t>
+          <t>['30', '37', '83', '86']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45712.625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.22</v>
+        <v>2.93</v>
       </c>
       <c r="M20" t="n">
-        <v>3.57</v>
+        <v>3.19</v>
       </c>
       <c r="N20" t="n">
-        <v>2.96</v>
+        <v>2.41</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['8', '39', '69']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AH20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI20" t="n">
         <v>2.25</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['30', '37', '83', '86']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45712.625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stal Stalowa Wola</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P21" t="n">
         <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '9', '38', '89']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '23', '67']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45712.625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.85</v>
       </c>
-      <c r="O24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['14', '29', '62', '87', '89']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45712.66666666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
         <v>5</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="Y25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.35</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['14', '29', '62', '87', '89']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AI25" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45712.66666666666</v>
@@ -4245,29 +4245,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R30" t="n">
         <v>1.57</v>
@@ -4305,31 +4305,31 @@
         <v>2.25</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X30" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC30" t="n">
         <v>2.1</v>
@@ -4339,25 +4339,25 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['2', '90+1']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45712.70833333334</v>
@@ -4374,29 +4374,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.9</v>
+        <v>2.81</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>2.64</v>
       </c>
       <c r="N31" t="n">
-        <v>1.85</v>
+        <v>2.97</v>
       </c>
       <c r="O31" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['2', '90+1']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['72', '89', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45712.70833333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,19 +4513,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA32" t="n">
         <v>3.75</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y32" t="n">
+      <c r="AB32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['72', '89', '90']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI32" t="n">
         <v>2.63</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['45+2']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45712.70833333334</v>
@@ -4761,35 +4761,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Vere United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>3.72</v>
+        <v>1.4</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q34" t="n">
-        <v>4.5</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="T34" t="n">
-        <v>4.5</v>
+        <v>2.19</v>
       </c>
       <c r="U34" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="V34" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>2.1</v>
+        <v>4.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.99</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.34</v>
+        <v>2.05</v>
       </c>
       <c r="AA34" t="n">
-        <v>6</v>
+        <v>2.41</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['3', '87']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.75</v>
+        <v>1.22</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45712.79166666666</v>
@@ -4890,119 +4890,119 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vere United</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P35" t="n">
         <v>2</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>6</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>7</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y35" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
+      <c r="Z35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.15</v>
       </c>
-      <c r="X35" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['3', '87']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.33</v>
+        <v>1.44</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.22</v>
+        <v>3.5</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45712.79166666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,19 +5029,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="M36" t="n">
-        <v>3.51</v>
+        <v>2.62</v>
       </c>
       <c r="N36" t="n">
-        <v>5.75</v>
+        <v>3.72</v>
       </c>
       <c r="O36" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="P36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.25</v>
-      </c>
       <c r="T36" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.1</v>
       </c>
-      <c r="W36" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y36" t="n">
+      <c r="AC36" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AD36" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45712.79166666666</v>
@@ -5277,29 +5277,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Real Kings</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -5309,65 +5309,65 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5376,20 +5376,20 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45712.83333333334</v>
@@ -5406,29 +5406,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Kings</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -5438,65 +5438,65 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5505,20 +5505,20 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45712.83333333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="M41" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>4.06</v>
       </c>
       <c r="O41" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="S41" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="T41" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z41" t="n">
         <v>1.44</v>
       </c>
-      <c r="X41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA41" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['45+2', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45712.875</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5829,28 +5829,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>4.06</v>
+        <v>5.1</v>
       </c>
       <c r="O42" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P42" t="n">
         <v>1.91</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S42" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T42" t="n">
         <v>4</v>
@@ -5862,50 +5862,50 @@
         <v>1.12</v>
       </c>
       <c r="W42" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="X42" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AA42" t="n">
         <v>5.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
+          <t>['37', '87']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
           <t>['59']</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45712.875</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
         <v>2</v>
       </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N43" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P43" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="S43" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="T43" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U43" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="X43" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AA43" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['37', '87']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['45+2', '85']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AJ43" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45712.875</v>
